--- a/files/九龙-启德-柏蔚森 I.xlsx
+++ b/files/九龙-启德-柏蔚森 I.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,19 +214,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,10 +232,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +637,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -14140,159 +14178,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚森 I - 5座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>216 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>194 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,485万
+$1485万
 $29,000/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 招标单位
@@ -14300,7 +14338,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -14308,7 +14346,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $744万
@@ -14316,7 +14354,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $725万
@@ -14324,7 +14362,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $702万
@@ -14332,15 +14370,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
-$1,079万
+$1079万
 $23,000/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $887万
@@ -14348,7 +14386,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -14357,13 +14395,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -14371,7 +14409,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 招标单位
@@ -14379,7 +14417,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -14387,7 +14425,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $736万
@@ -14395,7 +14433,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $703万
@@ -14403,7 +14441,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $689万
@@ -14411,7 +14449,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $844万
@@ -14419,7 +14457,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $821万
@@ -14427,7 +14465,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -14436,13 +14474,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -14450,7 +14488,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 招标单位
@@ -14458,7 +14496,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -14466,7 +14504,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $729万
@@ -14474,7 +14512,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $701万
@@ -14482,7 +14520,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $687万
@@ -14490,7 +14528,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $832万
@@ -14498,7 +14536,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $852万
@@ -14506,7 +14544,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -14515,13 +14553,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -14529,7 +14567,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 招标单位
@@ -14537,7 +14575,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -14545,7 +14583,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $722万
@@ -14553,7 +14591,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 招标单位
@@ -14561,7 +14599,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $685万
@@ -14569,7 +14607,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $819万
@@ -14577,7 +14615,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $789万
@@ -14585,7 +14623,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -14594,13 +14632,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -14608,7 +14646,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $885万
@@ -14616,7 +14654,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -14624,7 +14662,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $721万
@@ -14632,7 +14670,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $697万
@@ -14640,7 +14678,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $683万
@@ -14648,7 +14686,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $817万
@@ -14656,7 +14694,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $742万
@@ -14664,7 +14702,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $752万
@@ -14673,13 +14711,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -14687,7 +14725,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $868万
@@ -14695,15 +14733,15 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,301万
+$1301万
 $23,234/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $709万
@@ -14711,7 +14749,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $694万
@@ -14719,7 +14757,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $830万
@@ -14727,7 +14765,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $807万
@@ -14735,7 +14773,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $736万
@@ -14743,7 +14781,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $746万
@@ -14752,21 +14790,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,148万
+$1148万
 $22,430/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $826万
@@ -14774,15 +14812,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,239万
+$1239万
 $22,129/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $737万
@@ -14790,7 +14828,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $692万
@@ -14798,7 +14836,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $679万
@@ -14806,7 +14844,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $796万
@@ -14814,7 +14852,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $731万
@@ -14822,7 +14860,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $740万
@@ -14831,21 +14869,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,098万
+$1098万
 $21,451/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $821万
@@ -14853,15 +14891,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,230万
+$1230万
 $21,973/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $734万
@@ -14869,7 +14907,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $690万
@@ -14877,7 +14915,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $706万
@@ -14885,7 +14923,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $791万
@@ -14893,7 +14931,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $725万
@@ -14901,7 +14939,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $734万
@@ -14910,21 +14948,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,086万
+$1086万
 $21,215/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $812万
@@ -14932,15 +14970,15 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,204万
+$1204万
 $21,507/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $719万
@@ -14948,7 +14986,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $705万
@@ -14956,7 +14994,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $674万
@@ -14964,7 +15002,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $792万
@@ -14972,7 +15010,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $732万
@@ -14980,7 +15018,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $728万
@@ -14989,21 +15027,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,074万
+$1074万
 $20,980/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $803万
@@ -15011,15 +15049,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,191万
+$1191万
 $21,271/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $700万
@@ -15027,7 +15065,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $686万
@@ -15035,7 +15073,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $672万
@@ -15043,7 +15081,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $790万
@@ -15051,7 +15089,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $713万
@@ -15059,7 +15097,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $722万
@@ -15068,21 +15106,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,062万
+$1062万
 $20,750/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $794万
@@ -15090,15 +15128,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,178万
+$1178万
 $21,036/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $745万
@@ -15106,7 +15144,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $684万
@@ -15114,7 +15152,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $670万
@@ -15122,7 +15160,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $788万
@@ -15130,7 +15168,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $707万
@@ -15138,7 +15176,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $716万
@@ -15147,21 +15185,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,046万
+$1046万
 $20,439/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $780万
@@ -15169,15 +15207,15 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,173万
+$1173万
 $20,952/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $696万
@@ -15185,7 +15223,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $682万
@@ -15193,7 +15231,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $697万
@@ -15201,7 +15239,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $819万
@@ -15209,7 +15247,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $714万
@@ -15217,7 +15255,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $710万
@@ -15226,21 +15264,21 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,039万
+$1039万
 $20,285/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $771万
@@ -15248,15 +15286,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,159万
+$1159万
 $20,693/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $694万
@@ -15264,7 +15302,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $680万
@@ -15272,7 +15310,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $695万
@@ -15280,7 +15318,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $784万
@@ -15288,7 +15326,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $706万
@@ -15296,7 +15334,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $829万
@@ -15305,21 +15343,21 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,072万
+$1072万
 $20,941/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $763万
@@ -15327,15 +15365,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,142万
+$1142万
 $20,388/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $643万
@@ -15343,7 +15381,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $678万
@@ -15351,7 +15389,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $664万
@@ -15359,7 +15397,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $782万
@@ -15367,7 +15405,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $704万
@@ -15375,7 +15413,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $712万
@@ -15384,21 +15422,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,230万
+$1230万
 $24,014/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $784万
@@ -15406,15 +15444,15 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,122万
+$1122万
 $20,036/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $690万
@@ -15422,7 +15460,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $676万
@@ -15430,7 +15468,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $691万
@@ -15438,7 +15476,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $780万
@@ -15446,7 +15484,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $732万
@@ -15454,7 +15492,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $710万
@@ -15463,21 +15501,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,001万
+$1001万
 $19,553/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $779万
@@ -15485,15 +15523,15 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,162万
+$1162万
 $20,746/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $680万
@@ -15501,7 +15539,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $663万
@@ -15509,7 +15547,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $689万
@@ -15517,7 +15555,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $811万
@@ -15525,7 +15563,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $729万
@@ -15533,7 +15571,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $708万
@@ -15542,21 +15580,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,018万
+$1018万
 $19,893/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $742万
@@ -15564,15 +15602,15 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,106万
+$1106万
 $19,757/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $682万
@@ -15580,7 +15618,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $672万
@@ -15588,7 +15626,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $658万
@@ -15596,7 +15634,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $828万
@@ -15604,7 +15642,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $698万
@@ -15612,7 +15650,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $706万
@@ -15621,21 +15659,21 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,106万
+$1106万
 $21,596/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $736万
@@ -15643,15 +15681,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,146万
+$1146万
 $20,459/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $674万
@@ -15659,7 +15697,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $674万
@@ -15667,7 +15705,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $684万
@@ -15675,7 +15713,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $807万
@@ -15683,7 +15721,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $695万
@@ -15691,7 +15729,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $704万
@@ -15700,21 +15738,21 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1,024万
+$1024万
 $20,004/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $733万
@@ -15722,15 +15760,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,140万
+$1140万
 $20,354/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $645万
@@ -15738,7 +15776,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $672万
@@ -15746,7 +15784,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $683万
@@ -15754,7 +15792,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $805万
@@ -15762,7 +15800,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $682万
@@ -15770,7 +15808,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $710万
@@ -15779,13 +15817,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 $978万
@@ -15793,7 +15831,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $760万
@@ -15801,15 +15839,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,088万
+$1088万
 $19,425/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $686万
@@ -15817,7 +15855,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $643万
@@ -15825,7 +15863,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $653万
@@ -15833,7 +15871,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $770万
@@ -15841,7 +15879,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $672万
@@ -15849,7 +15887,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $680万
@@ -15858,13 +15896,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 $972万
@@ -15872,7 +15910,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $756万
@@ -15880,15 +15918,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,082万
+$1082万
 $19,330/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $782万
@@ -15896,7 +15934,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $641万
@@ -15904,7 +15942,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $651万
@@ -15912,7 +15950,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $768万
@@ -15920,7 +15958,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $646万
@@ -15928,7 +15966,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $667万
@@ -15937,13 +15975,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 $955万
@@ -15951,7 +15989,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $753万
@@ -15959,15 +15997,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,149万
+$1149万
 $20,523/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $666万
@@ -15975,7 +16013,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $639万
@@ -15983,7 +16021,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $649万
@@ -15991,7 +16029,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $766万
@@ -15999,7 +16037,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $642万
@@ -16007,7 +16045,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $650万
@@ -16016,13 +16054,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 $963万
@@ -16030,7 +16068,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $718万
@@ -16038,15 +16076,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,144万
+$1144万
 $20,421/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $637万
@@ -16054,7 +16092,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
 $637万
@@ -16062,7 +16100,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $647万
@@ -16070,7 +16108,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $797万
@@ -16078,7 +16116,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $639万
@@ -16086,7 +16124,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $647万
@@ -16095,13 +16133,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 $999万
@@ -16109,7 +16147,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 $715万
@@ -16117,15 +16155,15 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-$1,066万
+$1066万
 $19,041/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
 $635万
@@ -16133,7 +16171,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 353呎 (2房)
 $599万
@@ -16141,7 +16179,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $640万
@@ -16149,7 +16187,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
 $762万
@@ -16157,7 +16195,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
 $636万
@@ -16165,7 +16203,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 $644万
@@ -16176,7 +16214,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -16189,187 +16227,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚森 I - 6座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>75 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>73 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
 $939万
@@ -16377,7 +16415,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 380呎 (2房)
 $757万
@@ -16385,7 +16423,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 380呎 (2房)
 $791万
@@ -16393,7 +16431,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 380呎 (2房)
 $760万
@@ -16401,7 +16439,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 380呎 (2房)
 $810万
@@ -16409,7 +16447,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 381呎 (2房)
 $818万
@@ -16417,7 +16455,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 385呎 (2房)
 $832万
@@ -16425,7 +16463,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 288呎 (1房)
 $499万
@@ -16433,7 +16471,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>J | 272呎 (1房)
 $472万
@@ -16441,7 +16479,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>K | 276呎 (1房)
 $459万
@@ -16449,7 +16487,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>L | 276呎 (1房)
 $459万
@@ -16457,7 +16495,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>M | 276呎 (1房)
 $459万
@@ -16465,7 +16503,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>N | 276呎 (1房)
 $459万
@@ -16473,7 +16511,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="O6" s="16" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>P | 274呎 (1房)
 $456万
@@ -16481,7 +16519,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="P6" s="16" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr">
         <is>
           <t>Q | 382呎 (2房)
 $635万
@@ -16490,13 +16528,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
 $920万
@@ -16504,7 +16542,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 380呎 (2房)
 $760万
@@ -16512,7 +16550,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 380呎 (2房)
 $744万
@@ -16520,7 +16558,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 380呎 (2房)
 $745万
@@ -16528,7 +16566,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 380呎 (2房)
 $794万
@@ -16536,7 +16574,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 381呎 (2房)
 $802万
@@ -16544,7 +16582,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 385呎 (2房)
 $880万
@@ -16552,7 +16590,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 288呎 (1房)
 $469万
@@ -16560,7 +16598,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 272呎 (1房)
 $443万
@@ -16568,7 +16606,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 276呎 (1房)
 $472万
@@ -16576,7 +16614,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 276呎 (1房)
 $450万
@@ -16584,7 +16622,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 276呎 (1房)
 $469万
@@ -16592,7 +16630,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>N | 276呎 (1房)
 $450万
@@ -16600,7 +16638,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="O7" s="16" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>P | 274呎 (1房)
 $446万
@@ -16608,7 +16646,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>Q | 382呎 (2房)
 $623万
@@ -16617,13 +16655,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
 $751万
@@ -16631,7 +16669,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 380呎 (2房)
 $770万
@@ -16639,7 +16677,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 380呎 (2房)
 $740万
@@ -16647,7 +16685,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 380呎 (2房)
 $773万
@@ -16655,7 +16693,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 380呎 (2房)
 $820万
@@ -16663,7 +16701,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 381呎 (2房)
 $794万
@@ -16671,7 +16709,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 385呎 (2房)
 $808万
@@ -16679,7 +16717,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 288呎 (1房)
 $467万
@@ -16687,7 +16725,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 272呎 (1房)
 $441万
@@ -16695,7 +16733,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 276呎 (1房)
 $448万
@@ -16703,7 +16741,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 276呎 (1房)
 $448万
@@ -16711,7 +16749,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 276呎 (1房)
 $448万
@@ -16719,7 +16757,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>N | 276呎 (1房)
 $448万
@@ -16727,7 +16765,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="O8" s="16" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>P | 274呎 (1房)
 $463万
@@ -16735,7 +16773,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="P8" s="16" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
         <is>
           <t>Q | 382呎 (2房)
 $620万
@@ -16744,13 +16782,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
 $919万
@@ -16758,7 +16796,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 380呎 (2房)
 $735万
@@ -16766,7 +16804,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 380呎 (2房)
 $768万
@@ -16774,7 +16812,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 380呎 (2房)
 $769万
@@ -16782,7 +16820,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 380呎 (2房)
 $785万
@@ -16790,7 +16828,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 381呎 (2房)
 $793万
@@ -16798,7 +16836,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 385呎 (2房)
 $804万
@@ -16806,7 +16844,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 288呎 (1房)
 $465万
@@ -16814,7 +16852,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 272呎 (1房)
 $439万
@@ -16822,7 +16860,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 276呎 (1房)
 $445万
@@ -16830,7 +16868,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 276呎 (1房)
 $445万
@@ -16838,7 +16876,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 276呎 (1房)
 $445万
@@ -16846,7 +16884,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>N | 276呎 (1房)
 $445万
@@ -16854,7 +16892,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>P | 274呎 (1房)
 $442万
@@ -16862,7 +16900,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="P9" s="16" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>Q | 382呎 (2房)
 $616万
@@ -16871,13 +16909,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
 $743万
@@ -16885,7 +16923,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 380呎 (2房)
 $762万
@@ -16893,7 +16931,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 380呎 (2房)
 $764万
@@ -16901,7 +16939,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 380呎 (2房)
 $734万
@@ -16909,7 +16947,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 380呎 (2房)
 $768万
@@ -16917,7 +16955,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 381呎 (2房)
 $776万
@@ -16925,7 +16963,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 385呎 (2房)
 $797万
@@ -16933,7 +16971,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (1房)
 $416万
@@ -16941,7 +16979,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 234呎 (1房)
 $386万
@@ -16949,7 +16987,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 238呎 (1房)
 $396万
@@ -16957,7 +16995,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 239呎 (1房)
 $396万
@@ -16965,7 +17003,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 239呎 (1房)
 $396万
@@ -16973,7 +17011,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>N | 238呎 (1房)
 $412万
@@ -16981,7 +17019,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>P | 236呎 (1房)
 $408万
@@ -16989,7 +17027,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="P10" s="16" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>Q | 345呎 (2房)
 $648万
@@ -17000,7 +17038,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/九龙-启德-柏蔚森 I.xlsx
+++ b/files/九龙-启德-柏蔚森 I.xlsx
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J293"/>
+  <dimension ref="A1:N293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -637,9 +637,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -697,6 +701,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -747,6 +771,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -793,6 +837,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7273400</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>18892</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -839,6 +899,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8845340</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>18860</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -885,6 +961,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>5760500</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>14401</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -931,6 +1023,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5947460</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>15211</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -977,6 +1085,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>6099160</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>15559</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1027,6 +1151,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1077,6 +1221,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1123,6 +1287,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>12175360</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>23780</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1173,6 +1353,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1219,6 +1419,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6733840</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>17490</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1265,6 +1481,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>6922440</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>14760</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1311,6 +1543,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5648160</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>14120</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1357,6 +1605,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5762960</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>14739</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1403,6 +1667,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>6037660</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>15402</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1453,6 +1733,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1503,6 +1803,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1553,6 +1873,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1603,6 +1943,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1649,6 +2009,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>6990500</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>18157</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1695,6 +2071,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>6819120</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>14540</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1741,6 +2133,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5630940</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>14077</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1787,6 +2195,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5745740</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>14695</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1833,6 +2257,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5976980</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>15247</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1883,6 +2323,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1933,6 +2393,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1983,6 +2463,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2033,6 +2533,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2079,6 +2599,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>6472260</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>16811</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2125,6 +2661,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>6716620</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>14321</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2171,6 +2723,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>5614540</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>14036</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2221,6 +2789,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2267,6 +2855,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>5916300</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>15093</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2317,6 +2921,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2367,6 +2991,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2417,6 +3061,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2463,6 +3127,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6164760</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>16054</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2509,6 +3189,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6088500</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>15814</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2555,6 +3251,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>6697760</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>14281</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2601,6 +3313,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5597320</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>13993</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2647,6 +3375,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5712120</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>14609</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2693,6 +3437,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5915480</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>15091</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2743,6 +3503,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2789,6 +3569,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>7257000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>19404</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2839,6 +3635,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2885,6 +3701,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>6115560</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>15926</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2931,6 +3763,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>6039300</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>15686</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2977,6 +3825,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>6620680</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>14117</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3023,6 +3887,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6806820</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>17017</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3069,6 +3949,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>5694900</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>14565</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3115,6 +4011,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5810520</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>14823</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3161,6 +4073,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>10669020</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>19052</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3207,6 +4135,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>7115140</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>19024</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3257,6 +4201,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3303,6 +4267,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6066360</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>15798</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3349,6 +4329,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>5990920</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>15561</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3395,6 +4391,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6523100</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>13909</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3441,6 +4453,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>5564520</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>13911</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3487,6 +4515,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>5678500</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>14523</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3522,7 +4566,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3533,6 +4577,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>6040940</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>15411</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3579,6 +4639,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>10161440</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>18145</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3625,6 +4701,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>6776480</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>18119</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3671,6 +4763,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>9416880</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>18392</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3717,6 +4825,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6017160</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>15670</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3763,6 +4887,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>5942540</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>15435</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3809,6 +4949,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>6483740</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>13825</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3855,6 +5011,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5785100</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>14463</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3901,6 +5073,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5660460</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>14477</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3936,7 +5124,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3947,6 +5135,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>6022080</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>15362</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3993,6 +5197,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>10090100</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>18018</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4039,6 +5259,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>6728920</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>17992</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4085,6 +5321,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>9006060</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>17590</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4131,6 +5383,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>5968780</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>15544</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4177,6 +5445,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5999120</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>15582</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4223,6 +5507,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>6490300</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>13839</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4269,6 +5569,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5530900</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>13827</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4315,6 +5631,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5781000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>14785</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4361,6 +5693,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>5898260</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>15047</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4407,6 +5755,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>9876080</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>17636</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4453,6 +5817,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>6656760</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>17799</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4499,6 +5879,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>8906840</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>17396</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4545,6 +5941,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>5919580</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>15416</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4591,6 +6003,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>5846600</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>15186</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4637,6 +6065,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6474720</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>13805</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4683,6 +6127,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>5514500</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>13786</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4729,6 +6189,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5626840</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>14391</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4775,6 +6251,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>5740820</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>14645</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4821,6 +6313,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>9767840</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>17443</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4867,6 +6375,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>6583780</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>17604</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4913,6 +6437,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>8808440</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>17204</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4959,6 +6499,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5872840</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>15294</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5005,6 +6561,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>5799040</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>15062</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5051,6 +6623,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>6458320</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>13770</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5097,6 +6685,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>5498100</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>13745</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5143,6 +6747,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>5610440</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>14349</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5189,6 +6809,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>6107360</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>15580</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5235,6 +6871,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>9659600</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>17249</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5281,6 +6933,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>6511620</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>17411</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5327,6 +6995,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>8711680</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>17015</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5373,6 +7057,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>5825280</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>15170</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5408,7 +7108,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5419,6 +7119,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5857260</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>15214</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5465,6 +7181,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>6717440</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>14323</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5500,7 +7232,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5511,6 +7243,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5715400</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>14288</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5557,6 +7305,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5593220</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>14305</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5603,6 +7367,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>5707200</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>14559</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5649,6 +7429,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>9621060</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>17180</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5695,6 +7491,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>6392720</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>17093</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5741,6 +7553,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>8581300</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>16760</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5776,7 +7604,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5787,6 +7615,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>6796980</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>17700</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5833,6 +7677,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>5787560</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>15033</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5879,6 +7739,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>6426340</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>13702</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5925,6 +7801,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>5699000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>14248</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5971,6 +7863,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>5576820</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>14263</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6006,7 +7914,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6017,6 +7925,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>5689980</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>14515</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6063,6 +7987,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>9502160</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>16968</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6109,6 +8049,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>6320560</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>16900</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6155,6 +8111,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>8516520</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>16634</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6201,6 +8173,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>5842500</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>15215</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6247,6 +8235,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5770340</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>14988</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6293,6 +8297,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>6410760</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>13669</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6339,6 +8359,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5448900</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>13622</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6385,6 +8421,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>5560420</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>14221</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6420,7 +8472,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6431,6 +8483,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>5269320</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>13442</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6477,6 +8545,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>9361940</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>16718</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6523,6 +8607,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>6258240</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>16733</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6569,6 +8669,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>8792040</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>17172</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6615,6 +8731,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>5824460</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>15168</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6661,6 +8793,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>5999120</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>15582</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6707,6 +8855,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>6393540</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>13632</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6753,6 +8917,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>5664560</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>14161</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6799,6 +8979,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>5544020</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>14179</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6845,6 +9041,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>5655540</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>14427</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6891,6 +9103,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>9200400</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>16429</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6937,6 +9165,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>6429620</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>17191</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6983,6 +9227,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>10081900</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>19691</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7029,6 +9289,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>5807240</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>15123</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7075,6 +9351,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>5981080</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>15535</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7121,6 +9413,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6650200</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7167,6 +9475,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>5646520</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>14116</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7213,6 +9537,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>5434960</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7259,6 +9599,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>5572720</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>14216</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7305,6 +9661,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>9526760</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>17012</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7351,6 +9723,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>6384520</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>17071</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7397,6 +9785,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>8209020</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>16033</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7443,6 +9847,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>5790020</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>15078</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7489,6 +9909,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>5719500</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>14856</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7535,6 +9971,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6789600</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>14477</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7581,6 +10033,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>5399700</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>13499</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7627,6 +10095,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>5512040</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>14097</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7673,6 +10157,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>5596500</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>14277</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7719,6 +10219,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>9072480</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>16201</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7765,6 +10281,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>6080300</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>16257</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7811,6 +10343,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>8351700</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>16312</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7857,6 +10405,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>5771980</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>15031</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7903,6 +10467,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>5702280</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>14811</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7949,6 +10529,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>6617400</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>14110</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7995,6 +10591,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>5612900</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>14032</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8041,6 +10653,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>5527620</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>14137</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8087,6 +10715,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>5530900</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>14109</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8133,6 +10777,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>9394740</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>16776</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8179,6 +10839,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>6038480</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>16146</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8214,7 +10890,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8225,6 +10901,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>9066740</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>17708</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8271,6 +10963,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>5826100</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>15172</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8317,6 +11025,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>5594860</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>14532</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8363,6 +11087,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>6600180</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>14073</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8409,6 +11149,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>5597320</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>13993</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8455,6 +11211,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>5510400</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>14093</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8501,6 +11273,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>5287360</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>13488</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8547,6 +11335,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>9346360</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>16690</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8593,6 +11397,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>6007320</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>16062</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8639,6 +11459,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>8398440</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>16403</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8685,6 +11521,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>5576000</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>14521</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8731,6 +11583,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>5507120</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>14304</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8777,6 +11645,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>6314820</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>13464</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8823,6 +11707,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>5351320</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>13378</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8869,6 +11769,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>5269320</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>13477</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8915,6 +11831,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>5625200</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>14350</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8961,6 +11893,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>8919960</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>15928</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9007,6 +11955,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>6232820</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>16665</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9053,6 +12017,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>8015500</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>15655</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9099,6 +12079,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>5466120</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>14235</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9145,6 +12141,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>5293920</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>13750</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9191,6 +12203,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>6299240</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>13431</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9237,6 +12265,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>5335740</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>13339</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9272,7 +12316,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9283,6 +12327,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>5253740</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>13437</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9329,6 +12389,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>6410760</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>16354</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9375,6 +12451,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>8876500</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>15851</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9421,6 +12513,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>6202480</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>16584</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9467,6 +12575,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>7974500</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>15575</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9513,6 +12637,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>5334100</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>13891</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9559,6 +12699,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>5267680</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>13682</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9605,6 +12761,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>6283660</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>13398</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9651,6 +12823,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>5320160</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>13300</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9697,6 +12885,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>5238160</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>13397</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9743,6 +12947,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>5464480</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>13940</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9789,6 +13009,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>9424260</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>16829</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9835,6 +13071,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>6171320</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>16501</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9881,6 +13133,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>7830180</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>15293</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9927,6 +13195,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>5307860</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>13823</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9973,6 +13257,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>5240620</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>13612</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10019,6 +13319,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>6534580</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>13933</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10065,6 +13381,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>5303760</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>13259</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10111,6 +13443,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>5222580</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>13357</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10157,6 +13505,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>5225040</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>13329</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10203,6 +13567,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>9377520</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>16746</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10249,6 +13629,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>5889240</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>15747</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10295,6 +13691,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>7895780</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>15421</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10341,6 +13753,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>5279980</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>13750</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10387,6 +13815,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>5214380</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>13544</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10433,6 +13877,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>6251680</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>13330</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10479,6 +13939,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>5250460</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>13126</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10525,6 +14001,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>4910160</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>13910</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10571,6 +14063,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>5209460</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>13289</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10617,6 +14125,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>8743660</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>15614</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10663,6 +14187,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>5859720</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>15668</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10709,6 +14249,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>8191800</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10755,6 +14311,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>5207820</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>13633</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10801,6 +14373,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>3735100</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>13632</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10847,6 +14435,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>3762160</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>13631</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10893,6 +14497,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>3762160</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>13631</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10939,6 +14559,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>3762160</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>13631</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10985,6 +14621,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>3762160</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>13631</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11020,7 +14672,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11031,6 +14683,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>3866300</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>14214</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11077,6 +14745,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>4093440</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>14213</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11123,6 +14807,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>6824860</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>17727</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11169,6 +14869,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>6709240</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>17610</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11215,6 +14931,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>6642820</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>17481</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11261,6 +14993,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>6229540</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>16394</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11307,6 +15055,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>6484560</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>17065</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11353,6 +15117,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>6208220</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>16337</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11399,6 +15179,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7698980</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>19997</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11445,6 +15241,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>5105320</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>13365</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11491,6 +15303,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>3661300</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>13362</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11537,6 +15365,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>3688360</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>13364</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11583,6 +15427,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>3845800</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>13934</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11629,6 +15489,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>3688360</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>13364</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11675,6 +15551,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>3872860</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>14032</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11721,6 +15613,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>3635060</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>13364</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11767,6 +15675,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>3849080</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>13365</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11813,6 +15737,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>7216000</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>18743</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11859,6 +15799,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>6577220</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>17263</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11905,6 +15861,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>6511620</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>17136</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11951,6 +15923,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>6107360</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>16072</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11997,6 +15985,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>6096700</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>16044</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12043,6 +16047,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>6234460</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>16406</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12089,6 +16109,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>7547280</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>19603</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12135,6 +16171,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>5080720</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>13300</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12181,6 +16233,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>3799060</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>13865</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12227,6 +16295,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>3669500</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>13295</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12273,6 +16357,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>3669500</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>13295</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12319,6 +16419,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>3669500</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>13295</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12365,6 +16481,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>3669500</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>13295</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12411,6 +16543,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>3617020</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>13298</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12457,6 +16605,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>3830220</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>13299</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12503,6 +16667,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>6624780</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>17207</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12549,6 +16729,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>6512440</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>17093</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12595,6 +16791,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>6723180</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>17693</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12641,6 +16853,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>6336960</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>16676</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12687,6 +16915,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>6067180</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>15966</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12733,6 +16977,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>6314820</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>16618</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12779,6 +17039,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>6156560</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>15991</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12825,6 +17101,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>5055300</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>13234</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12871,6 +17163,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>3625220</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>13231</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12906,7 +17214,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -12917,6 +17225,22 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>3651460</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>13230</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12963,6 +17287,22 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>3651460</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>13230</v>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13009,6 +17349,22 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>3651460</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>13230</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13055,6 +17411,22 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>3651460</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>13230</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13101,6 +17473,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>3598980</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>13232</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13147,6 +17535,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>3810540</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>13231</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13193,6 +17597,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>6591980</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>17122</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13239,6 +17659,22 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>6501780</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>17065</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13285,6 +17721,22 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>6437820</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>16942</v>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13320,7 +17772,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13331,6 +17783,22 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>6305800</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>16594</v>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13377,6 +17845,22 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>6295140</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>16566</v>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13423,6 +17907,22 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K277" s="5" t="n">
+        <v>6025360</v>
+      </c>
+      <c r="L277" s="5" t="n">
+        <v>15856</v>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13469,6 +17969,22 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>7534980</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>19571</v>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13515,6 +18031,22 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>5309500</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>15390</v>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13561,6 +18093,22 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>3347240</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>14183</v>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13607,6 +18155,22 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>3381680</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>14209</v>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13653,6 +18217,22 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>3251300</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>13604</v>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13699,6 +18279,22 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>3251300</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>13604</v>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13745,6 +18341,22 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>3243100</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>13626</v>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13791,6 +18403,22 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>3168480</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>13541</v>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13837,6 +18465,22 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>3407920</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>13577</v>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13883,6 +18527,22 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>6536220</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>16977</v>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13929,6 +18589,22 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>6364840</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>16706</v>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13975,6 +18651,22 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>6300060</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>16579</v>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14021,6 +18713,22 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>6016340</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>15832</v>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14067,6 +18775,22 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>6263160</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>16482</v>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14113,6 +18837,22 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>6251680</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>16452</v>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14159,13 +18899,29 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>6095880</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>15833</v>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -14327,7 +19083,7 @@
           <t>A | 512呎 (3房)
 $1485万
 $29,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -14351,7 +19107,7 @@
           <t>D | 392呎 (2房)
 $744万
 $18,974/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -14359,7 +19115,7 @@
           <t>E | 391呎 (2房)
 $725万
 $18,550/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -14367,7 +19123,7 @@
           <t>F | 400呎 (2房)
 $702万
 $17,562/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -14375,7 +19131,7 @@
           <t>G | 469呎 (2房)
 $1079万
 $23,000/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -14383,7 +19139,7 @@
           <t>H | 385呎 (2房)
 $887万
 $23,039/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -14430,7 +19186,7 @@
           <t>D | 392呎 (2房)
 $736万
 $18,783/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -14438,7 +19194,7 @@
           <t>E | 391呎 (2房)
 $703万
 $17,974/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -14446,7 +19202,7 @@
           <t>F | 400呎 (2房)
 $689万
 $17,220/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -14454,7 +19210,7 @@
           <t>G | 469呎 (2房)
 $844万
 $18,000/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -14462,7 +19218,7 @@
           <t>H | 385呎 (2房)
 $821万
 $21,330/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -14509,7 +19265,7 @@
           <t>D | 392呎 (2房)
 $729万
 $18,594/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -14517,7 +19273,7 @@
           <t>E | 391呎 (2房)
 $701万
 $17,921/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -14525,7 +19281,7 @@
           <t>F | 400呎 (2房)
 $687万
 $17,168/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -14533,7 +19289,7 @@
           <t>G | 469呎 (2房)
 $832万
 $17,731/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -14541,7 +19297,7 @@
           <t>H | 385呎 (2房)
 $852万
 $22,143/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -14588,7 +19344,7 @@
           <t>D | 392呎 (2房)
 $722万
 $18,406/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -14604,7 +19360,7 @@
           <t>F | 400呎 (2房)
 $685万
 $17,118/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -14612,7 +19368,7 @@
           <t>G | 469呎 (2房)
 $819万
 $17,465/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -14620,7 +19376,7 @@
           <t>H | 385呎 (2房)
 $789万
 $20,501/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -14651,7 +19407,7 @@
           <t>B | 374呎 (2房)
 $885万
 $23,663/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -14667,7 +19423,7 @@
           <t>D | 392呎 (2房)
 $721万
 $18,403/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -14675,7 +19431,7 @@
           <t>E | 391呎 (2房)
 $697万
 $17,816/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -14683,7 +19439,7 @@
           <t>F | 400呎 (2房)
 $683万
 $17,065/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -14691,7 +19447,7 @@
           <t>G | 469呎 (2房)
 $817万
 $17,416/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -14699,7 +19455,7 @@
           <t>H | 385呎 (2房)
 $742万
 $19,286/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -14707,7 +19463,7 @@
           <t>J | 384呎 (2房)
 $752万
 $19,578/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -14730,7 +19486,7 @@
           <t>B | 374呎 (2房)
 $868万
 $23,201/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -14738,7 +19494,7 @@
           <t>C | 560呎 (3房)
 $1301万
 $23,234/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -14746,7 +19502,7 @@
           <t>D | 392呎 (2房)
 $709万
 $18,077/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -14754,7 +19510,7 @@
           <t>E | 391呎 (2房)
 $694万
 $17,762/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -14770,7 +19526,7 @@
           <t>G | 469呎 (2房)
 $807万
 $17,215/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -14778,7 +19534,7 @@
           <t>H | 385呎 (2房)
 $736万
 $19,130/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -14786,7 +19542,7 @@
           <t>J | 384呎 (2房)
 $746万
 $19,422/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -14801,7 +19557,7 @@
           <t>A | 512呎 (3房)
 $1148万
 $22,430/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -14809,7 +19565,7 @@
           <t>B | 374呎 (2房)
 $826万
 $22,096/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -14817,7 +19573,7 @@
           <t>C | 560呎 (3房)
 $1239万
 $22,129/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -14825,7 +19581,7 @@
           <t>D | 392呎 (2房)
 $737万
 $18,793/呎
-(24年-07月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -14833,7 +19589,7 @@
           <t>E | 391呎 (2房)
 $692万
 $17,711/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -14841,7 +19597,7 @@
           <t>F | 400呎 (2房)
 $679万
 $16,965/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -14849,7 +19605,7 @@
           <t>G | 469呎 (2房)
 $796万
 $16,962/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -14857,7 +19613,7 @@
           <t>H | 385呎 (2房)
 $731万
 $18,977/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -14865,7 +19621,7 @@
           <t>J | 384呎 (2房)
 $740万
 $19,266/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -14880,7 +19636,7 @@
           <t>A | 512呎 (3房)
 $1098万
 $21,451/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14888,7 +19644,7 @@
           <t>B | 374呎 (2房)
 $821万
 $21,941/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -14896,7 +19652,7 @@
           <t>C | 560呎 (3房)
 $1230万
 $21,973/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -14904,7 +19660,7 @@
           <t>D | 392呎 (2房)
 $734万
 $18,735/呎
-(24年-07月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -14912,7 +19668,7 @@
           <t>E | 391呎 (2房)
 $690万
 $17,655/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -14920,7 +19676,7 @@
           <t>F | 400呎 (2房)
 $706万
 $17,638/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -14928,7 +19684,7 @@
           <t>G | 469呎 (2房)
 $791万
 $16,859/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -14936,7 +19692,7 @@
           <t>H | 385呎 (2房)
 $725万
 $18,823/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -14944,7 +19700,7 @@
           <t>J | 384呎 (2房)
 $734万
 $19,109/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -14959,7 +19715,7 @@
           <t>A | 512呎 (3房)
 $1086万
 $21,215/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -14967,7 +19723,7 @@
           <t>B | 374呎 (2房)
 $812万
 $21,706/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -14975,7 +19731,7 @@
           <t>C | 560呎 (3房)
 $1204万
 $21,507/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -14983,7 +19739,7 @@
           <t>D | 392呎 (2房)
 $719万
 $18,349/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -14991,7 +19747,7 @@
           <t>E | 391呎 (2房)
 $705万
 $18,031/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -14999,7 +19755,7 @@
           <t>F | 400呎 (2房)
 $674万
 $16,862/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -15007,7 +19763,7 @@
           <t>G | 469呎 (2房)
 $792万
 $16,876/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -15015,7 +19771,7 @@
           <t>H | 385呎 (2房)
 $732万
 $19,003/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -15023,7 +19779,7 @@
           <t>J | 384呎 (2房)
 $728万
 $18,956/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -15038,7 +19794,7 @@
           <t>A | 512呎 (3房)
 $1074万
 $20,980/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -15046,7 +19802,7 @@
           <t>B | 374呎 (2房)
 $803万
 $21,468/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -15054,7 +19810,7 @@
           <t>C | 560呎 (3房)
 $1191万
 $21,271/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -15062,7 +19818,7 @@
           <t>D | 392呎 (2房)
 $700万
 $17,860/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -15070,7 +19826,7 @@
           <t>E | 391呎 (2房)
 $686万
 $17,550/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -15078,7 +19834,7 @@
           <t>F | 400呎 (2房)
 $672万
 $16,812/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -15086,7 +19842,7 @@
           <t>G | 469呎 (2房)
 $790万
 $16,836/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -15094,7 +19850,7 @@
           <t>H | 385呎 (2房)
 $713万
 $18,519/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -15102,7 +19858,7 @@
           <t>J | 384呎 (2房)
 $722万
 $18,799/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -15117,7 +19873,7 @@
           <t>A | 512呎 (3房)
 $1062万
 $20,750/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -15125,7 +19881,7 @@
           <t>B | 374呎 (2房)
 $794万
 $21,233/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -15133,7 +19889,7 @@
           <t>C | 560呎 (3房)
 $1178万
 $21,036/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -15141,7 +19897,7 @@
           <t>D | 392呎 (2房)
 $745万
 $19,000/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -15149,7 +19905,7 @@
           <t>E | 391呎 (2房)
 $684万
 $17,499/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -15157,7 +19913,7 @@
           <t>F | 400呎 (2房)
 $670万
 $16,762/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -15165,7 +19921,7 @@
           <t>G | 469呎 (2房)
 $788万
 $16,793/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -15173,7 +19929,7 @@
           <t>H | 385呎 (2房)
 $707万
 $18,369/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -15181,7 +19937,7 @@
           <t>J | 384呎 (2房)
 $716万
 $18,651/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -15196,7 +19952,7 @@
           <t>A | 512呎 (3房)
 $1046万
 $20,439/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -15204,7 +19960,7 @@
           <t>B | 374呎 (2房)
 $780万
 $20,845/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -15212,7 +19968,7 @@
           <t>C | 560呎 (3房)
 $1173万
 $20,952/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -15220,7 +19976,7 @@
           <t>D | 392呎 (2房)
 $696万
 $17,755/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -15228,7 +19984,7 @@
           <t>E | 391呎 (2房)
 $682万
 $17,445/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -15236,7 +19992,7 @@
           <t>F | 400呎 (2房)
 $697万
 $17,425/呎
-(24年-07月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -15244,7 +20000,7 @@
           <t>G | 469呎 (2房)
 $819万
 $17,467/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -15252,7 +20008,7 @@
           <t>H | 385呎 (2房)
 $714万
 $18,553/呎
-(24年-08月)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -15260,7 +20016,7 @@
           <t>J | 384呎 (2房)
 $710万
 $18,500/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -15275,7 +20031,7 @@
           <t>A | 512呎 (3房)
 $1039万
 $20,285/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -15283,7 +20039,7 @@
           <t>B | 374呎 (2房)
 $771万
 $20,610/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -15291,7 +20047,7 @@
           <t>C | 560呎 (3房)
 $1159万
 $20,693/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -15299,7 +20055,7 @@
           <t>D | 392呎 (2房)
 $694万
 $17,702/呎
-(24年-07月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -15307,7 +20063,7 @@
           <t>E | 391呎 (2房)
 $680万
 $17,394/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -15315,7 +20071,7 @@
           <t>F | 400呎 (2房)
 $695万
 $17,375/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -15323,7 +20079,7 @@
           <t>G | 469呎 (2房)
 $784万
 $16,710/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -15331,7 +20087,7 @@
           <t>H | 385呎 (2房)
 $706万
 $18,332/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -15339,7 +20095,7 @@
           <t>J | 384呎 (2房)
 $829万
 $21,586/呎
-(26年-06月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -15354,7 +20110,7 @@
           <t>A | 512呎 (3房)
 $1072万
 $20,941/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -15362,7 +20118,7 @@
           <t>B | 374呎 (2房)
 $763万
 $20,406/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -15370,7 +20126,7 @@
           <t>C | 560呎 (3房)
 $1142万
 $20,388/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -15378,7 +20134,7 @@
           <t>D | 392呎 (2房)
 $643万
 $16,393/呎
-(24年-07月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -15386,7 +20142,7 @@
           <t>E | 391呎 (2房)
 $678万
 $17,343/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -15394,7 +20150,7 @@
           <t>F | 400呎 (2房)
 $664万
 $16,612/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -15402,7 +20158,7 @@
           <t>G | 469呎 (2房)
 $782万
 $16,670/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -15410,7 +20166,7 @@
           <t>H | 385呎 (2房)
 $704万
 $18,278/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -15418,7 +20174,7 @@
           <t>J | 384呎 (2房)
 $712万
 $18,555/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -15441,7 +20197,7 @@
           <t>B | 374呎 (2房)
 $784万
 $20,965/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -15449,7 +20205,7 @@
           <t>C | 560呎 (3房)
 $1122万
 $20,036/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -15457,7 +20213,7 @@
           <t>D | 392呎 (2房)
 $690万
 $17,594/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -15465,7 +20221,7 @@
           <t>E | 391呎 (2房)
 $676万
 $17,292/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -15473,7 +20229,7 @@
           <t>F | 400呎 (2房)
 $691万
 $17,270/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -15481,7 +20237,7 @@
           <t>G | 469呎 (2房)
 $780万
 $16,625/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -15489,7 +20245,7 @@
           <t>H | 385呎 (2房)
 $732万
 $19,003/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -15497,7 +20253,7 @@
           <t>J | 384呎 (2房)
 $710万
 $18,497/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -15512,7 +20268,7 @@
           <t>A | 512呎 (3房)
 $1001万
 $19,553/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -15520,7 +20276,7 @@
           <t>B | 374呎 (2房)
 $779万
 $20,818/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -15528,7 +20284,7 @@
           <t>C | 560呎 (3房)
 $1162万
 $20,746/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -15536,7 +20292,7 @@
           <t>D | 392呎 (2房)
 $680万
 $17,337/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -15544,7 +20300,7 @@
           <t>E | 391呎 (2房)
 $663万
 $16,951/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -15552,7 +20308,7 @@
           <t>F | 400呎 (2房)
 $689万
 $17,215/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -15560,7 +20316,7 @@
           <t>G | 469呎 (2房)
 $811万
 $17,292/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -15568,7 +20324,7 @@
           <t>H | 385呎 (2房)
 $729万
 $18,945/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -15576,7 +20332,7 @@
           <t>J | 384呎 (2房)
 $708万
 $18,443/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -15591,7 +20347,7 @@
           <t>A | 512呎 (3房)
 $1018万
 $19,893/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -15599,7 +20355,7 @@
           <t>B | 374呎 (2房)
 $742万
 $19,826/呎
-(24年-07月)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -15607,7 +20363,7 @@
           <t>C | 560呎 (3房)
 $1106万
 $19,757/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -15615,7 +20371,7 @@
           <t>D | 392呎 (2房)
 $682万
 $17,411/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -15623,7 +20379,7 @@
           <t>E | 391呎 (2房)
 $672万
 $17,192/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -15631,7 +20387,7 @@
           <t>F | 400呎 (2房)
 $658万
 $16,462/呎
-(24年-07月)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -15639,7 +20395,7 @@
           <t>G | 469呎 (2房)
 $828万
 $17,655/呎
-(24年-07月)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -15647,7 +20403,7 @@
           <t>H | 385呎 (2房)
 $698万
 $18,117/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -15655,7 +20411,7 @@
           <t>J | 384呎 (2房)
 $706万
 $18,388/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -15670,7 +20426,7 @@
           <t>A | 512呎 (3房)
 $1106万
 $21,596/呎
-(26年-06月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -15678,7 +20434,7 @@
           <t>B | 374呎 (2房)
 $736万
 $19,690/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -15686,7 +20442,7 @@
           <t>C | 560呎 (3房)
 $1146万
 $20,459/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -15694,7 +20450,7 @@
           <t>D | 392呎 (2房)
 $674万
 $17,207/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -15702,7 +20458,7 @@
           <t>E | 391呎 (2房)
 $674万
 $17,240/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -15710,7 +20466,7 @@
           <t>F | 400呎 (2房)
 $684万
 $17,112/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -15718,7 +20474,7 @@
           <t>G | 469呎 (2房)
 $807万
 $17,207/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -15726,7 +20482,7 @@
           <t>H | 385呎 (2房)
 $695万
 $18,062/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -15734,7 +20490,7 @@
           <t>J | 384呎 (2房)
 $704万
 $18,331/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -15749,7 +20505,7 @@
           <t>A | 512呎 (3房)
 $1024万
 $20,004/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -15757,7 +20513,7 @@
           <t>B | 374呎 (2房)
 $733万
 $19,588/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -15765,7 +20521,7 @@
           <t>C | 560呎 (3房)
 $1140万
 $20,354/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -15773,7 +20529,7 @@
           <t>D | 392呎 (2房)
 $645万
 $16,449/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -15781,7 +20537,7 @@
           <t>E | 391呎 (2房)
 $672万
 $17,187/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -15789,7 +20545,7 @@
           <t>F | 400呎 (2房)
 $683万
 $17,065/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -15797,7 +20553,7 @@
           <t>G | 469呎 (2房)
 $805万
 $17,162/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -15805,7 +20561,7 @@
           <t>H | 385呎 (2房)
 $682万
 $17,722/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -15813,7 +20569,7 @@
           <t>J | 384呎 (2房)
 $710万
 $18,503/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -15828,7 +20584,7 @@
           <t>A | 512呎 (3房)
 $978万
 $19,092/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -15836,7 +20592,7 @@
           <t>B | 374呎 (2房)
 $760万
 $20,324/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -15844,7 +20600,7 @@
           <t>C | 560呎 (3房)
 $1088万
 $19,425/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -15852,7 +20608,7 @@
           <t>D | 392呎 (2房)
 $686万
 $17,500/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -15860,7 +20616,7 @@
           <t>E | 391呎 (2房)
 $643万
 $16,435/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -15868,7 +20624,7 @@
           <t>F | 400呎 (2房)
 $653万
 $16,315/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -15876,7 +20632,7 @@
           <t>G | 469呎 (2房)
 $770万
 $16,420/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -15884,7 +20640,7 @@
           <t>H | 385呎 (2房)
 $672万
 $17,444/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -15892,7 +20648,7 @@
           <t>J | 384呎 (2房)
 $680万
 $17,708/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -15907,7 +20663,7 @@
           <t>A | 512呎 (3房)
 $972万
 $18,994/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -15915,7 +20671,7 @@
           <t>B | 374呎 (2房)
 $756万
 $20,225/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -15923,7 +20679,7 @@
           <t>C | 560呎 (3房)
 $1082万
 $19,330/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -15939,7 +20695,7 @@
           <t>E | 391呎 (2房)
 $641万
 $16,386/呎
-(24年-07月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -15947,7 +20703,7 @@
           <t>F | 400呎 (2房)
 $651万
 $16,268/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -15955,7 +20711,7 @@
           <t>G | 469呎 (2房)
 $768万
 $16,380/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -15963,7 +20719,7 @@
           <t>H | 385呎 (2房)
 $646万
 $16,769/呎
-(25年-03月)</t>
+(25年-03月-09日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -15971,7 +20727,7 @@
           <t>J | 384呎 (2房)
 $667万
 $17,359/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -15986,7 +20742,7 @@
           <t>A | 512呎 (3房)
 $955万
 $18,650/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -15994,7 +20750,7 @@
           <t>B | 374呎 (2房)
 $753万
 $20,123/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -16002,7 +20758,7 @@
           <t>C | 560呎 (3房)
 $1149万
 $20,523/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -16010,7 +20766,7 @@
           <t>D | 392呎 (2房)
 $666万
 $17,000/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -16018,7 +20774,7 @@
           <t>E | 391呎 (2房)
 $639万
 $16,338/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -16026,7 +20782,7 @@
           <t>F | 400呎 (2房)
 $649万
 $16,220/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -16034,7 +20790,7 @@
           <t>G | 469呎 (2房)
 $766万
 $16,339/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -16042,7 +20798,7 @@
           <t>H | 385呎 (2房)
 $642万
 $16,686/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -16050,7 +20806,7 @@
           <t>J | 384呎 (2房)
 $650万
 $16,940/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -16065,7 +20821,7 @@
           <t>A | 512呎 (3房)
 $963万
 $18,807/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -16073,7 +20829,7 @@
           <t>B | 374呎 (2房)
 $718万
 $19,203/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -16081,7 +20837,7 @@
           <t>C | 560呎 (3房)
 $1144万
 $20,421/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -16089,7 +20845,7 @@
           <t>D | 392呎 (2房)
 $637万
 $16,255/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -16097,7 +20853,7 @@
           <t>E | 391呎 (2房)
 $637万
 $16,289/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -16105,7 +20861,7 @@
           <t>F | 400呎 (2房)
 $647万
 $16,170/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -16113,7 +20869,7 @@
           <t>G | 469呎 (2房)
 $797万
 $16,991/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -16121,7 +20877,7 @@
           <t>H | 385呎 (2房)
 $639万
 $16,600/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -16129,7 +20885,7 @@
           <t>J | 384呎 (2房)
 $647万
 $16,857/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -16144,7 +20900,7 @@
           <t>A | 512呎 (3房)
 $999万
 $19,512/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -16152,7 +20908,7 @@
           <t>B | 374呎 (2房)
 $715万
 $19,107/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -16160,7 +20916,7 @@
           <t>C | 560呎 (3房)
 $1066万
 $19,041/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -16168,7 +20924,7 @@
           <t>D | 392呎 (2房)
 $635万
 $16,207/呎
-(24年-08月)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -16176,7 +20932,7 @@
           <t>E | 353呎 (2房)
 $599万
 $16,963/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -16184,7 +20940,7 @@
           <t>F | 400呎 (2房)
 $640万
 $16,008/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -16192,7 +20948,7 @@
           <t>G | 469呎 (2房)
 $762万
 $16,256/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -16200,7 +20956,7 @@
           <t>H | 385呎 (2房)
 $636万
 $16,517/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -16208,7 +20964,7 @@
           <t>J | 384呎 (2房)
 $644万
 $16,768/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -16420,7 +21176,7 @@
           <t>B | 380呎 (2房)
 $757万
 $19,924/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -16428,7 +21184,7 @@
           <t>C | 380呎 (2房)
 $791万
 $20,811/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -16436,7 +21192,7 @@
           <t>D | 380呎 (2房)
 $760万
 $19,992/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -16444,7 +21200,7 @@
           <t>E | 380呎 (2房)
 $810万
 $21,318/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -16452,7 +21208,7 @@
           <t>F | 381呎 (2房)
 $818万
 $21,475/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -16460,7 +21216,7 @@
           <t>G | 385呎 (2房)
 $832万
 $21,618/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -16468,7 +21224,7 @@
           <t>H | 288呎 (1房)
 $499万
 $17,333/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -16476,7 +21232,7 @@
           <t>J | 272呎 (1房)
 $472万
 $17,335/呎
-(24年-07月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -16484,7 +21240,7 @@
           <t>K | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -16492,7 +21248,7 @@
           <t>L | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -16500,7 +21256,7 @@
           <t>M | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -16508,7 +21264,7 @@
           <t>N | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
@@ -16516,7 +21272,7 @@
           <t>P | 274呎 (1房)
 $456万
 $16,624/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
@@ -16524,7 +21280,7 @@
           <t>Q | 382呎 (2房)
 $635万
 $16,626/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -16547,7 +21303,7 @@
           <t>B | 380呎 (2房)
 $760万
 $20,008/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -16555,7 +21311,7 @@
           <t>C | 380呎 (2房)
 $744万
 $19,566/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -16563,7 +21319,7 @@
           <t>D | 380呎 (2房)
 $745万
 $19,600/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -16571,7 +21327,7 @@
           <t>E | 380呎 (2房)
 $794万
 $20,897/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -16579,7 +21335,7 @@
           <t>F | 381呎 (2房)
 $802万
 $21,052/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -16587,7 +21343,7 @@
           <t>G | 385呎 (2房)
 $880万
 $22,857/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -16595,7 +21351,7 @@
           <t>H | 288呎 (1房)
 $469万
 $16,299/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -16603,7 +21359,7 @@
           <t>J | 272呎 (1房)
 $443万
 $16,298/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -16611,7 +21367,7 @@
           <t>K | 276呎 (1房)
 $472万
 $17,112/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -16619,7 +21375,7 @@
           <t>L | 276呎 (1房)
 $450万
 $16,297/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -16627,7 +21383,7 @@
           <t>M | 276呎 (1房)
 $469万
 $16,993/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -16635,7 +21391,7 @@
           <t>N | 276呎 (1房)
 $450万
 $16,297/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="O6" s="20" t="inlineStr">
@@ -16643,7 +21399,7 @@
           <t>P | 274呎 (1房)
 $446万
 $16,296/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="P6" s="20" t="inlineStr">
@@ -16651,7 +21407,7 @@
           <t>Q | 382呎 (2房)
 $623万
 $16,298/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -16666,7 +21422,7 @@
           <t>A | 385呎 (2房)
 $751万
 $19,501/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -16674,7 +21430,7 @@
           <t>B | 380呎 (2房)
 $770万
 $20,266/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -16682,7 +21438,7 @@
           <t>C | 380呎 (2房)
 $740万
 $19,471/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -16690,7 +21446,7 @@
           <t>D | 380呎 (2房)
 $773万
 $20,337/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -16698,7 +21454,7 @@
           <t>E | 380呎 (2房)
 $820万
 $21,576/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -16706,7 +21462,7 @@
           <t>F | 381呎 (2房)
 $794万
 $20,845/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -16714,7 +21470,7 @@
           <t>G | 385呎 (2房)
 $808万
 $20,984/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -16722,7 +21478,7 @@
           <t>H | 288呎 (1房)
 $467万
 $16,219/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -16730,7 +21486,7 @@
           <t>J | 272呎 (1房)
 $441万
 $16,217/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -16738,7 +21494,7 @@
           <t>K | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -16746,7 +21502,7 @@
           <t>L | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -16754,7 +21510,7 @@
           <t>M | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -16762,7 +21518,7 @@
           <t>N | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -16770,7 +21526,7 @@
           <t>P | 274呎 (1房)
 $463万
 $16,909/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="P7" s="20" t="inlineStr">
@@ -16778,7 +21534,7 @@
           <t>Q | 382呎 (2房)
 $620万
 $16,220/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -16793,7 +21549,7 @@
           <t>A | 385呎 (2房)
 $919万
 $23,868/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -16801,7 +21557,7 @@
           <t>B | 380呎 (2房)
 $735万
 $19,337/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -16809,7 +21565,7 @@
           <t>C | 380呎 (2房)
 $768万
 $20,203/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -16817,7 +21573,7 @@
           <t>D | 380呎 (2房)
 $769万
 $20,237/呎
-(24年-07月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -16825,7 +21581,7 @@
           <t>E | 380呎 (2房)
 $785万
 $20,661/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -16833,7 +21589,7 @@
           <t>F | 381呎 (2房)
 $793万
 $20,811/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -16841,7 +21597,7 @@
           <t>G | 385呎 (2房)
 $804万
 $20,881/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -16849,7 +21605,7 @@
           <t>H | 288呎 (1房)
 $465万
 $16,135/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -16857,7 +21613,7 @@
           <t>J | 272呎 (1房)
 $439万
 $16,136/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -16865,7 +21621,7 @@
           <t>K | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -16873,7 +21629,7 @@
           <t>L | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -16881,7 +21637,7 @@
           <t>M | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -16889,7 +21645,7 @@
           <t>N | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-07月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -16897,7 +21653,7 @@
           <t>P | 274呎 (1房)
 $442万
 $16,135/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -16905,7 +21661,7 @@
           <t>Q | 382呎 (2房)
 $616万
 $16,139/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -16920,7 +21676,7 @@
           <t>A | 385呎 (2房)
 $743万
 $19,309/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -16928,7 +21684,7 @@
           <t>B | 380呎 (2房)
 $762万
 $20,063/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -16936,7 +21692,7 @@
           <t>C | 380呎 (2房)
 $764万
 $20,100/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -16944,7 +21700,7 @@
           <t>D | 380呎 (2房)
 $734万
 $19,308/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -16952,7 +21708,7 @@
           <t>E | 380呎 (2房)
 $768万
 $20,218/呎
-(25年-01月)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -16960,7 +21716,7 @@
           <t>F | 381呎 (2房)
 $776万
 $20,373/呎
-(25年-01月)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -16968,7 +21724,7 @@
           <t>G | 385呎 (2房)
 $797万
 $20,704/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -16976,7 +21732,7 @@
           <t>H | 251呎 (1房)
 $416万
 $16,558/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -16984,7 +21740,7 @@
           <t>J | 234呎 (1房)
 $386万
 $16,513/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -16992,7 +21748,7 @@
           <t>K | 238呎 (1房)
 $396万
 $16,618/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -17000,7 +21756,7 @@
           <t>L | 239呎 (1房)
 $396万
 $16,590/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -17008,7 +21764,7 @@
           <t>M | 239呎 (1房)
 $396万
 $16,590/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -17016,7 +21772,7 @@
           <t>N | 238呎 (1房)
 $412万
 $17,328/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -17024,7 +21780,7 @@
           <t>P | 236呎 (1房)
 $408万
 $17,297/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -17032,7 +21788,7 @@
           <t>Q | 345呎 (2房)
 $648万
 $18,768/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
